--- a/originales/respuestas/2025/01. Calificadas/bucle p17/Capital Salud.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p17/Capital Salud.xlsx
@@ -4,12 +4,13 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="p1" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="66BQj0wNezF0xldeGK+oMJg3gIscjDAwtpae7Nj6v04="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="0xcAsq7wnQLCr7DoLwgja8eNLWOoTC6AR6EL/PcGyEk="/>
     </ext>
   </extLst>
 </workbook>
@@ -108,6 +109,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -306,6 +311,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>

--- a/originales/respuestas/2025/01. Calificadas/bucle p17/Capital Salud.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p17/Capital Salud.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Entidad Nombre</t>
   </si>
@@ -29,6 +29,21 @@
   </si>
   <si>
     <t>Seleccione a quién estaba orientado cada canal</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C5</t>
   </si>
   <si>
     <t>Capital Salud</t>
@@ -48,7 +63,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -58,6 +73,11 @@
     <font>
       <sz val="11.0"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -92,14 +112,20 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -345,19 +371,49 @@
         <v>3</v>
       </c>
       <c r="E1" s="1"/>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>2.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
